--- a/Test Scenarios/Test Scenarios.xlsx
+++ b/Test Scenarios/Test Scenarios.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="118">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -147,6 +147,39 @@
     <t>Leave</t>
   </si>
   <si>
+    <t>TS039</t>
+  </si>
+  <si>
+    <t>TS040</t>
+  </si>
+  <si>
+    <t>TS041</t>
+  </si>
+  <si>
+    <t>TS042</t>
+  </si>
+  <si>
+    <t>TS043</t>
+  </si>
+  <si>
+    <t>TS044</t>
+  </si>
+  <si>
+    <t>TS045</t>
+  </si>
+  <si>
+    <t>TS046</t>
+  </si>
+  <si>
+    <t>TS047</t>
+  </si>
+  <si>
+    <t>TS048</t>
+  </si>
+  <si>
+    <t>TS049</t>
+  </si>
+  <si>
     <t>Time</t>
   </si>
   <si>
@@ -156,15 +189,9 @@
     <t>My Info</t>
   </si>
   <si>
-    <t>Search &amp; Filter</t>
-  </si>
-  <si>
     <t>Security</t>
   </si>
   <si>
-    <t>File Upload</t>
-  </si>
-  <si>
     <t>UI &amp; Usability</t>
   </si>
   <si>
@@ -255,9 +282,6 @@
     <t>Verify Search Functionality</t>
   </si>
   <si>
-    <t>Verify Filter Functionality</t>
-  </si>
-  <si>
     <t>Verify Authentication Security</t>
   </si>
   <si>
@@ -270,15 +294,6 @@
     <t>Verify Input Validation Security</t>
   </si>
   <si>
-    <t>Verify File Upload Functionality</t>
-  </si>
-  <si>
-    <t>Verify File Download Functionality</t>
-  </si>
-  <si>
-    <t>Verify File Deletion Functionality</t>
-  </si>
-  <si>
     <t>Verify UI Elements and Layout</t>
   </si>
   <si>
@@ -295,6 +310,69 @@
   </si>
   <si>
     <t>Verify Employee Leave Workflow End-to-End</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Verify Employee Reviews Search Functionality</t>
+  </si>
+  <si>
+    <t>Verify Review Filter Functionality</t>
+  </si>
+  <si>
+    <t>Verify Review Records Display and Management Functionality</t>
+  </si>
+  <si>
+    <t>Directory</t>
+  </si>
+  <si>
+    <t>Verify Employee Directory Search Functionality</t>
+  </si>
+  <si>
+    <t>Verify Employee Directory Filter Functionality</t>
+  </si>
+  <si>
+    <t>Verify Employee Directory Information Display Functionality</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Verify Purge Employee Records Functionality</t>
+  </si>
+  <si>
+    <t>Verify Maintenance Access Records Functionality</t>
+  </si>
+  <si>
+    <t>Verify Maintenance Module Access Control</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>Verify Claim Submission and Assignment Functionality</t>
+  </si>
+  <si>
+    <t>Verify Employee Claims Search and Tracking Functionality</t>
+  </si>
+  <si>
+    <t>Verify Claim Approval and Status Management Functionality</t>
+  </si>
+  <si>
+    <t>Buzz</t>
+  </si>
+  <si>
+    <t>Verify Post Creation and Sharing Functionality</t>
+  </si>
+  <si>
+    <t>Verify Post Interaction Functionality (Like, Comment, Share)</t>
+  </si>
+  <si>
+    <t>Verify Buzz Feed Content Display and Management Functionality</t>
+  </si>
+  <si>
+    <t>Search</t>
   </si>
 </sst>
 </file>
@@ -626,12 +704,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -650,10 +728,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -661,10 +739,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -672,10 +750,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -683,10 +761,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -694,10 +772,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -705,10 +783,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -716,10 +794,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -727,10 +805,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -738,10 +816,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -752,7 +830,7 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -763,7 +841,7 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -774,7 +852,7 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -782,10 +860,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -793,10 +871,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -804,10 +882,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -815,10 +893,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -826,10 +904,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -837,10 +915,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -848,10 +926,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -859,10 +937,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -870,10 +948,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -881,10 +959,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -892,10 +970,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -903,10 +981,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -914,10 +992,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -925,10 +1003,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -936,10 +1014,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -947,10 +1025,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -958,10 +1036,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -969,10 +1047,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -980,87 +1058,208 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>34</v>
       </c>
-      <c r="B33" t="s">
-        <v>47</v>
+      <c r="B33" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>35</v>
       </c>
-      <c r="B34" t="s">
-        <v>47</v>
+      <c r="B34" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>36</v>
       </c>
-      <c r="B35" t="s">
-        <v>48</v>
+      <c r="B35" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>37</v>
       </c>
-      <c r="B36" t="s">
-        <v>48</v>
+      <c r="B36" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>38</v>
       </c>
-      <c r="B37" t="s">
-        <v>48</v>
+      <c r="B37" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>39</v>
       </c>
-      <c r="B38" t="s">
-        <v>48</v>
+      <c r="B38" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
         <v>90</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Test Scenarios/Test Scenarios.xlsx
+++ b/Test Scenarios/Test Scenarios.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -705,14 +705,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,7 +723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -734,7 +734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -745,7 +745,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -756,7 +756,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -767,7 +767,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -778,7 +778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -789,7 +789,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -800,7 +800,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -811,7 +811,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -822,7 +822,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -833,7 +833,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -844,7 +844,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -855,7 +855,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -866,7 +866,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -877,7 +877,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -888,7 +888,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -899,7 +899,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -910,7 +910,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -921,7 +921,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -932,7 +932,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -943,7 +943,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -954,7 +954,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -965,7 +965,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -976,7 +976,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -987,7 +987,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -998,7 +998,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
